--- a/data/skus.xlsx
+++ b/data/skus.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>酱包小包1</t>
+          <t>酱包小包装1</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>酱包小包2</t>
+          <t>酱包小包装2</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>酱包小包3</t>
+          <t>酱包小包装3</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>酱包小包4</t>
+          <t>酱包小包装4</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>酱包小包5</t>
+          <t>酱包小包装5</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -578,7 +578,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>酱包小包6</t>
+          <t>酱包小包装6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>酱包小包7</t>
+          <t>酱包小包装7</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>酱包小包8</t>
+          <t>酱包小包装8</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -647,7 +647,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>酱包小包9</t>
+          <t>酱包小包装9</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -670,7 +670,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>酱包小包10</t>
+          <t>酱包小包装10</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -969,7 +969,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>粉包小包1</t>
+          <t>粉包小包装1</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>粉包小包2</t>
+          <t>粉包小包装2</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>粉包小包3</t>
+          <t>粉包小包装3</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>粉包小包4</t>
+          <t>粉包小包装4</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>粉包小包5</t>
+          <t>粉包小包装5</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>粉包小包6</t>
+          <t>粉包小包装6</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>粉包小包7</t>
+          <t>粉包小包装7</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>粉包小包8</t>
+          <t>粉包小包装8</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>粉包小包9</t>
+          <t>粉包小包装9</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>粉包小包10</t>
+          <t>粉包小包装10</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>菜包小包1</t>
+          <t>菜包小包装1</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>菜包小包2</t>
+          <t>菜包小包装2</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>菜包小包3</t>
+          <t>菜包小包装3</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜包小包4</t>
+          <t>菜包小包装4</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>菜包小包5</t>
+          <t>菜包小包装5</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>菜包小包6</t>
+          <t>菜包小包装6</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>菜包小包7</t>
+          <t>菜包小包装7</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>菜包小包8</t>
+          <t>菜包小包装8</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>菜包小包9</t>
+          <t>菜包小包装9</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>菜包小包10</t>
+          <t>菜包小包装10</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1714,7 +1714,11 @@
       <c r="D56" t="n">
         <v>10</v>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1733,7 +1737,11 @@
       <c r="D57" t="n">
         <v>10</v>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1752,7 +1760,11 @@
       <c r="D58" t="n">
         <v>10</v>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1771,7 +1783,11 @@
       <c r="D59" t="n">
         <v>10</v>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1790,7 +1806,11 @@
       <c r="D60" t="n">
         <v>10</v>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1809,7 +1829,11 @@
       <c r="D61" t="n">
         <v>10</v>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1828,7 +1852,11 @@
       <c r="D62" t="n">
         <v>10</v>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1847,7 +1875,11 @@
       <c r="D63" t="n">
         <v>10</v>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1866,7 +1898,11 @@
       <c r="D64" t="n">
         <v>10</v>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1885,7 +1921,11 @@
       <c r="D65" t="n">
         <v>10</v>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1904,7 +1944,11 @@
       <c r="D66" t="n">
         <v>10</v>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1923,7 +1967,11 @@
       <c r="D67" t="n">
         <v>10</v>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1942,7 +1990,11 @@
       <c r="D68" t="n">
         <v>10</v>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1961,7 +2013,11 @@
       <c r="D69" t="n">
         <v>10</v>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1980,7 +2036,11 @@
       <c r="D70" t="n">
         <v>10</v>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1999,7 +2059,11 @@
       <c r="D71" t="n">
         <v>10</v>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2018,7 +2082,11 @@
       <c r="D72" t="n">
         <v>10</v>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2037,7 +2105,11 @@
       <c r="D73" t="n">
         <v>10</v>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2056,7 +2128,11 @@
       <c r="D74" t="n">
         <v>10</v>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2075,7 +2151,11 @@
       <c r="D75" t="n">
         <v>10</v>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2094,7 +2174,11 @@
       <c r="D76" t="n">
         <v>100</v>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2113,7 +2197,11 @@
       <c r="D77" t="n">
         <v>100</v>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2132,7 +2220,11 @@
       <c r="D78" t="n">
         <v>100</v>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2151,7 +2243,11 @@
       <c r="D79" t="n">
         <v>100</v>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2170,7 +2266,11 @@
       <c r="D80" t="n">
         <v>100</v>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2189,7 +2289,11 @@
       <c r="D81" t="n">
         <v>100</v>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2208,7 +2312,11 @@
       <c r="D82" t="n">
         <v>100</v>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2227,7 +2335,11 @@
       <c r="D83" t="n">
         <v>100</v>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2246,7 +2358,11 @@
       <c r="D84" t="n">
         <v>100</v>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2265,7 +2381,11 @@
       <c r="D85" t="n">
         <v>100</v>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2275,7 +2395,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>成品1</t>
+          <t>成品面1</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2284,7 +2404,11 @@
       <c r="D86" t="n">
         <v>5</v>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>箱</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2294,7 +2418,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>成品2</t>
+          <t>成品面2</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2303,7 +2427,11 @@
       <c r="D87" t="n">
         <v>5</v>
       </c>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>箱</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2313,7 +2441,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>成品3</t>
+          <t>成品面3</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2322,7 +2450,11 @@
       <c r="D88" t="n">
         <v>5</v>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>箱</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2332,7 +2464,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>成品4</t>
+          <t>成品面4</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2341,7 +2473,11 @@
       <c r="D89" t="n">
         <v>5</v>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>箱</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2351,7 +2487,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>成品5</t>
+          <t>成品面5</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2360,7 +2496,11 @@
       <c r="D90" t="n">
         <v>5</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>箱</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2370,7 +2510,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>成品6</t>
+          <t>成品面6</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2379,7 +2519,11 @@
       <c r="D91" t="n">
         <v>5</v>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>箱</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2389,7 +2533,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>成品7</t>
+          <t>成品面7</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2398,7 +2542,11 @@
       <c r="D92" t="n">
         <v>5</v>
       </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>箱</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2408,7 +2556,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>成品8</t>
+          <t>成品面8</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2417,7 +2565,11 @@
       <c r="D93" t="n">
         <v>5</v>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>箱</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2427,7 +2579,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>成品9</t>
+          <t>成品面9</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2436,7 +2588,11 @@
       <c r="D94" t="n">
         <v>5</v>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>箱</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2446,7 +2602,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>成品10</t>
+          <t>成品面10</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2455,7 +2611,11 @@
       <c r="D95" t="n">
         <v>5</v>
       </c>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>箱</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
